--- a/Sindhi Muslim/Salary Sheet/Staff Record.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Staff Record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA53ECE-CE6E-4F80-8DEA-2747A59D586E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D25888A-7ED1-4A45-8209-D239927DDB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attandance" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="99">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -52,18 +52,6 @@
     <t>Designation</t>
   </si>
   <si>
-    <t>PRESENTY</t>
-  </si>
-  <si>
-    <t>ABSENTY</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>PL</t>
-  </si>
-  <si>
     <t>P.DAYS</t>
   </si>
   <si>
@@ -320,6 +308,30 @@
   </si>
   <si>
     <t>Non-Teaching Staff</t>
+  </si>
+  <si>
+    <t>Hussan Bano</t>
+  </si>
+  <si>
+    <t>Muhammad Mashooq</t>
+  </si>
+  <si>
+    <t>42301-5768818-8</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>Haleema</t>
+  </si>
+  <si>
+    <t>Abdul Sattar</t>
+  </si>
+  <si>
+    <t>41105-4725771-0</t>
   </si>
 </sst>
 </file>
@@ -329,8 +341,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd"/>
-    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -453,7 +465,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -673,19 +685,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -730,6 +729,45 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -740,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -771,9 +809,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -782,6 +817,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -792,124 +857,181 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1268,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AM23"/>
+  <dimension ref="A2:AM25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1276,20 +1398,17 @@
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
     <col min="5" max="34" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="8" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -1414,13 +1533,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="19" t="s">
+      <c r="AI3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="19"/>
-      <c r="AK3" s="19"/>
-      <c r="AL3" s="19"/>
-      <c r="AM3" s="20"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="29"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1525,20 +1644,20 @@
       <c r="AH4" s="9">
         <v>45596</v>
       </c>
-      <c r="AI4" s="4" t="s">
+      <c r="AI4" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL4" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM4" s="78" t="s">
         <v>5</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM4" s="12" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1547,87 +1666,113 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P5" s="10"/>
       <c r="Q5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
+      <c r="X5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
+      <c r="AE5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI5" s="10">
         <f>COUNTIF(D5:AH5,"P")</f>
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AJ5" s="10">
         <f>COUNTIF(D5:AH5,"A")</f>
         <v>0</v>
       </c>
       <c r="AK5" s="10">
-        <f>COUNTIF(D5:AH5,"SL")</f>
+        <f>COUNTIF(D5:AH5,"L")</f>
         <v>0</v>
       </c>
       <c r="AL5" s="10">
         <f>COUNTBLANK(D5:AH5)</f>
-        <v>17</v>
-      </c>
-      <c r="AM5" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM5" s="12">
         <f>AI5+AK5+AL5</f>
         <v>31</v>
       </c>
@@ -1638,180 +1783,232 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P6" s="10"/>
       <c r="Q6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
+      <c r="X6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="10"/>
-      <c r="AG6" s="10"/>
-      <c r="AH6" s="10"/>
+      <c r="AE6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI6" s="10">
-        <f t="shared" ref="AI6:AI12" si="1">COUNTIF(D6:AH6,"P")</f>
-        <v>14</v>
+        <f t="shared" ref="AI6:AI13" si="1">COUNTIF(D6:AH6,"P")</f>
+        <v>27</v>
       </c>
       <c r="AJ6" s="10">
-        <f t="shared" ref="AJ6:AJ12" si="2">COUNTIF(D6:AH6,"A")</f>
+        <f t="shared" ref="AJ6:AJ13" si="2">COUNTIF(D6:AH6,"A")</f>
         <v>0</v>
       </c>
       <c r="AK6" s="10">
-        <f t="shared" ref="AK6:AK12" si="3">COUNTIF(D6:AH6,"SL")</f>
+        <f t="shared" ref="AK6:AK12" si="3">COUNTIF(D6:AH6,"L")</f>
         <v>0</v>
       </c>
       <c r="AL6" s="10">
-        <f t="shared" ref="AL6:AL12" si="4">COUNTBLANK(D6:AH6)</f>
-        <v>17</v>
-      </c>
-      <c r="AM6" s="13">
-        <f t="shared" ref="AM6:AM12" si="5">AI6+AK6+AL6</f>
+        <f t="shared" ref="AL6:AL13" si="4">COUNTBLANK(D6:AH6)</f>
+        <v>4</v>
+      </c>
+      <c r="AM6" s="12">
+        <f t="shared" ref="AM6:AM13" si="5">AI6+AK6+AL6</f>
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <f t="shared" ref="A7:A12" si="6">IF(B7="","",A6+1)</f>
+        <f t="shared" ref="A7:A11" si="6">IF(B7="","",A6+1)</f>
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
+      <c r="X7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
+      <c r="AE7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH7" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="AI7" s="10">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK7" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="10">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM7" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="12">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1820,87 +2017,113 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
+      <c r="X8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
+      <c r="AE8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH8" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI8" s="10">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" s="10">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM8" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="12">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
@@ -1911,89 +2134,115 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
-      <c r="AC9" s="10"/>
+      <c r="X9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD9" s="10"/>
-      <c r="AE9" s="10"/>
-      <c r="AF9" s="10"/>
-      <c r="AG9" s="10"/>
-      <c r="AH9" s="10"/>
+      <c r="AE9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH9" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI9" s="10">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" s="10">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM9" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="12">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -2002,73 +2251,99 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
+      <c r="X10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
+      <c r="AE10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH10" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI10" s="10">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="2"/>
@@ -2080,9 +2355,9 @@
       </c>
       <c r="AL10" s="10">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM10" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM10" s="12">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
@@ -2093,73 +2368,99 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
+      <c r="X11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
+      <c r="AE11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI11" s="10">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AJ11" s="10">
         <f t="shared" si="2"/>
@@ -2171,712 +2472,840 @@
       </c>
       <c r="AL11" s="10">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM11" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM11" s="12">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A12" s="73">
+        <v>8</v>
+      </c>
+      <c r="B12" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="75"/>
+      <c r="Q12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="75"/>
+      <c r="X12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD12" s="75"/>
+      <c r="AE12" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF12" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH12" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI12" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="10">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="11"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="11">
+      <c r="AK12" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AM12" s="12">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI13" s="11">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="AJ12" s="11">
+        <v>26</v>
+      </c>
+      <c r="AJ13" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="11">
+      <c r="AK13" s="11">
+        <f>COUNTIF(D13:AH13,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AL13" s="11">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="AM12" s="14">
+        <v>4</v>
+      </c>
+      <c r="AM13" s="13">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:39" ht="27" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="8" t="str">
-        <f>TEXT(D17,"ddd")</f>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="8" t="str">
+        <f>TEXT(D18,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="E16" s="8" t="str">
-        <f t="shared" ref="E16:AH16" si="7">TEXT(E17,"ddd")</f>
+      <c r="E17" s="8" t="str">
+        <f t="shared" ref="E17:AH17" si="7">TEXT(E18,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="F16" s="8" t="str">
+      <c r="F17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="G16" s="8" t="str">
+      <c r="G17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="H16" s="8" t="str">
+      <c r="H17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="I16" s="8" t="str">
+      <c r="I17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="J16" s="8" t="str">
+      <c r="J17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="K16" s="8" t="str">
+      <c r="K17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="L16" s="8" t="str">
+      <c r="L17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="M16" s="8" t="str">
+      <c r="M17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="N16" s="8" t="str">
+      <c r="N17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="O16" s="8" t="str">
+      <c r="O17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="P16" s="8" t="str">
+      <c r="P17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="Q16" s="8" t="str">
+      <c r="Q17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="R16" s="8" t="str">
+      <c r="R17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="S16" s="8" t="str">
+      <c r="S17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="T16" s="8" t="str">
+      <c r="T17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="U16" s="8" t="str">
+      <c r="U17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="V16" s="8" t="str">
+      <c r="V17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="W16" s="8" t="str">
+      <c r="W17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="X16" s="8" t="str">
+      <c r="X17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="Y16" s="8" t="str">
+      <c r="Y17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="Z16" s="8" t="str">
+      <c r="Z17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="AA16" s="8" t="str">
+      <c r="AA17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AB16" s="8" t="str">
+      <c r="AB17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Fri</v>
       </c>
-      <c r="AC16" s="8" t="str">
+      <c r="AC17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sat</v>
       </c>
-      <c r="AD16" s="8" t="str">
+      <c r="AD17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Sun</v>
       </c>
-      <c r="AE16" s="8" t="str">
+      <c r="AE17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Mon</v>
       </c>
-      <c r="AF16" s="8" t="str">
+      <c r="AF17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Tue</v>
       </c>
-      <c r="AG16" s="8" t="str">
+      <c r="AG17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Wed</v>
       </c>
-      <c r="AH16" s="8" t="str">
+      <c r="AH17" s="8" t="str">
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AI16" s="19" t="s">
+      <c r="AI17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="19"/>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="20"/>
-    </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="9">
-        <v>45566</v>
-      </c>
-      <c r="E17" s="9">
-        <v>45567</v>
-      </c>
-      <c r="F17" s="9">
-        <v>45568</v>
-      </c>
-      <c r="G17" s="9">
-        <v>45569</v>
-      </c>
-      <c r="H17" s="9">
-        <v>45570</v>
-      </c>
-      <c r="I17" s="9">
-        <v>45571</v>
-      </c>
-      <c r="J17" s="9">
-        <v>45572</v>
-      </c>
-      <c r="K17" s="9">
-        <v>45573</v>
-      </c>
-      <c r="L17" s="9">
-        <v>45574</v>
-      </c>
-      <c r="M17" s="9">
-        <v>45575</v>
-      </c>
-      <c r="N17" s="9">
-        <v>45576</v>
-      </c>
-      <c r="O17" s="9">
-        <v>45577</v>
-      </c>
-      <c r="P17" s="9">
-        <v>45578</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>45579</v>
-      </c>
-      <c r="R17" s="9">
-        <v>45580</v>
-      </c>
-      <c r="S17" s="9">
-        <v>45581</v>
-      </c>
-      <c r="T17" s="9">
-        <v>45582</v>
-      </c>
-      <c r="U17" s="9">
-        <v>45583</v>
-      </c>
-      <c r="V17" s="9">
-        <v>45584</v>
-      </c>
-      <c r="W17" s="9">
-        <v>45585</v>
-      </c>
-      <c r="X17" s="9">
-        <v>45586</v>
-      </c>
-      <c r="Y17" s="9">
-        <v>45587</v>
-      </c>
-      <c r="Z17" s="9">
-        <v>45588</v>
-      </c>
-      <c r="AA17" s="9">
-        <v>45589</v>
-      </c>
-      <c r="AB17" s="9">
-        <v>45590</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>45591</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>45592</v>
-      </c>
-      <c r="AE17" s="9">
-        <v>45593</v>
-      </c>
-      <c r="AF17" s="9">
-        <v>45594</v>
-      </c>
-      <c r="AG17" s="9">
-        <v>45595</v>
-      </c>
-      <c r="AH17" s="9">
-        <v>45596</v>
-      </c>
-      <c r="AI17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM17" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="28"/>
+      <c r="AL17" s="28"/>
+      <c r="AM17" s="29"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <f>IF(B18="","",1)</f>
-        <v>1</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="R18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
-      <c r="AI18" s="10">
-        <f>COUNTIF(D18:AH18,"P")</f>
-        <v>14</v>
-      </c>
-      <c r="AJ18" s="10">
-        <f>COUNTIF(D18:AH18,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="10">
-        <f>COUNTIF(D18:AH18,"SL")</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="10">
-        <f>COUNTBLANK(D18:AH18)</f>
-        <v>17</v>
-      </c>
-      <c r="AM18" s="13">
-        <f>AI18+AK18+AL18</f>
-        <v>31</v>
+      <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9">
+        <v>45566</v>
+      </c>
+      <c r="E18" s="9">
+        <v>45567</v>
+      </c>
+      <c r="F18" s="9">
+        <v>45568</v>
+      </c>
+      <c r="G18" s="9">
+        <v>45569</v>
+      </c>
+      <c r="H18" s="9">
+        <v>45570</v>
+      </c>
+      <c r="I18" s="9">
+        <v>45571</v>
+      </c>
+      <c r="J18" s="9">
+        <v>45572</v>
+      </c>
+      <c r="K18" s="9">
+        <v>45573</v>
+      </c>
+      <c r="L18" s="9">
+        <v>45574</v>
+      </c>
+      <c r="M18" s="9">
+        <v>45575</v>
+      </c>
+      <c r="N18" s="9">
+        <v>45576</v>
+      </c>
+      <c r="O18" s="9">
+        <v>45577</v>
+      </c>
+      <c r="P18" s="9">
+        <v>45578</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>45579</v>
+      </c>
+      <c r="R18" s="9">
+        <v>45580</v>
+      </c>
+      <c r="S18" s="9">
+        <v>45581</v>
+      </c>
+      <c r="T18" s="9">
+        <v>45582</v>
+      </c>
+      <c r="U18" s="9">
+        <v>45583</v>
+      </c>
+      <c r="V18" s="9">
+        <v>45584</v>
+      </c>
+      <c r="W18" s="9">
+        <v>45585</v>
+      </c>
+      <c r="X18" s="9">
+        <v>45586</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>45587</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>45588</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>45589</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>45590</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>45591</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>45592</v>
+      </c>
+      <c r="AE18" s="9">
+        <v>45593</v>
+      </c>
+      <c r="AF18" s="9">
+        <v>45594</v>
+      </c>
+      <c r="AG18" s="9">
+        <v>45595</v>
+      </c>
+      <c r="AH18" s="9">
+        <v>45596</v>
+      </c>
+      <c r="AI18" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ18" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK18" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL18" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM18" s="78" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f>IF(B19="","",A18+1)</f>
-        <v>2</v>
+        <f>IF(B19="","",1)</f>
+        <v>1</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V19" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
-      <c r="AC19" s="10"/>
+      <c r="X19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC19" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD19" s="10"/>
-      <c r="AE19" s="10"/>
-      <c r="AF19" s="10"/>
-      <c r="AG19" s="10"/>
-      <c r="AH19" s="10"/>
+      <c r="AE19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH19" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI19" s="10">
-        <f t="shared" ref="AI19:AI23" si="8">COUNTIF(D19:AH19,"P")</f>
-        <v>14</v>
+        <f>COUNTIF(D19:AH19,"P")</f>
+        <v>25</v>
       </c>
       <c r="AJ19" s="10">
-        <f t="shared" ref="AJ19:AJ23" si="9">COUNTIF(D19:AH19,"A")</f>
+        <f>COUNTIF(D19:AH19,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="AK19" s="10">
+        <f>COUNTIF(D19:AH19,"SL")</f>
         <v>0</v>
       </c>
-      <c r="AK19" s="10">
-        <f t="shared" ref="AK19:AK23" si="10">COUNTIF(D19:AH19,"SL")</f>
-        <v>0</v>
-      </c>
       <c r="AL19" s="10">
-        <f t="shared" ref="AL19:AL23" si="11">COUNTBLANK(D19:AH19)</f>
-        <v>17</v>
-      </c>
-      <c r="AM19" s="13">
-        <f t="shared" ref="AM19:AM23" si="12">AI19+AK19+AL19</f>
-        <v>31</v>
+        <f>COUNTBLANK(D19:AH19)</f>
+        <v>4</v>
+      </c>
+      <c r="AM19" s="12">
+        <f>AI19+AK19+AL19</f>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" ref="A20:A23" si="13">IF(B20="","",A19+1)</f>
-        <v>3</v>
+        <f>IF(B20="","",A19+1)</f>
+        <v>2</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V20" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
+      <c r="X20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC20" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
+      <c r="AE20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH20" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI20" s="10">
-        <f t="shared" si="8"/>
-        <v>14</v>
+        <f t="shared" ref="AI20:AI25" si="8">COUNTIF(D20:AH20,"P")</f>
+        <v>27</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="AJ20:AJ25" si="9">COUNTIF(D20:AH20,"A")</f>
         <v>0</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="AK20:AK25" si="10">COUNTIF(D20:AH20,"SL")</f>
         <v>0</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="AM20" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="AL20:AL25" si="11">COUNTBLANK(D20:AH20)</f>
+        <v>4</v>
+      </c>
+      <c r="AM20" s="12">
+        <f t="shared" ref="AM20:AM25" si="12">AI20+AK20+AL20</f>
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" ref="A21:A23" si="13">IF(B21="","",A20+1)</f>
+        <v>3</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V21" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
-      <c r="AC21" s="10"/>
+      <c r="X21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC21" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AD21" s="10"/>
-      <c r="AE21" s="10"/>
-      <c r="AF21" s="10"/>
-      <c r="AG21" s="10"/>
-      <c r="AH21" s="10"/>
+      <c r="AE21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH21" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="AI21" s="10">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AJ21" s="10">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="10"/>
@@ -2884,90 +3313,116 @@
       </c>
       <c r="AL21" s="10">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="AM21" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="12">
         <f t="shared" si="12"/>
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
+        <v>8</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
-      <c r="AB22" s="10"/>
-      <c r="AC22" s="10"/>
+      <c r="X22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="AD22" s="10"/>
-      <c r="AE22" s="10"/>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10"/>
-      <c r="AH22" s="10"/>
+      <c r="AE22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="AI22" s="10">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AJ22" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="10"/>
@@ -2975,100 +3430,358 @@
       </c>
       <c r="AL22" s="10">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="AM22" s="13">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="12">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="T23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="U23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="V23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="AJ23" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="AM23" s="12">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="R23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="11"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="11">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A24" s="73">
+        <v>6</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="N24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="R24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="S24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="T24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="75"/>
+      <c r="X24" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH24" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI24" s="75">
         <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="AJ23" s="11">
+        <v>9</v>
+      </c>
+      <c r="AJ24" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="11">
+      <c r="AK24" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="11">
+      <c r="AL24" s="75">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="AM23" s="14">
+        <v>4</v>
+      </c>
+      <c r="AM24" s="76">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>7</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI25" s="11">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="AJ25" s="11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="11">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="AM25" s="13">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
@@ -3077,15 +3790,15 @@
   <mergeCells count="4">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="AI3:AM3"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="AI16:AM16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="AI17:AM17"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:AH12">
+  <conditionalFormatting sqref="D3:AH13">
     <cfRule type="expression" dxfId="8" priority="4">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:AH12">
+  <conditionalFormatting sqref="D5:AH13">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
@@ -3093,12 +3806,12 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:AH23">
+  <conditionalFormatting sqref="D17:AH25">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:AH23">
+  <conditionalFormatting sqref="D19:AH25">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
@@ -3112,11 +3825,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
@@ -3132,853 +3845,987 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="61"/>
+      <c r="A1" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="40" t="s">
+      <c r="I3" s="42" t="s">
         <v>38</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>42</v>
       </c>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
       <c r="L3" s="42"/>
-      <c r="M3" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="N3" s="44" t="s">
-        <v>13</v>
+      <c r="M3" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="46"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="52"/>
+      <c r="N4" s="34"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="45"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="46"/>
+    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="71"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="31">
+      <c r="A6" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="81">
         <v>44774</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="34">
+      <c r="F6" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="84">
         <v>22000</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="80">
         <v>31</v>
       </c>
-      <c r="J6" s="15">
-        <f>Attandance!AI5</f>
-        <v>14</v>
-      </c>
-      <c r="K6" s="15">
+      <c r="J6" s="80">
+        <f>Attandance!AM5</f>
+        <v>31</v>
+      </c>
+      <c r="K6" s="80">
         <f>Attandance!AJ5</f>
         <v>0</v>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="80">
         <f>Attandance!AK5</f>
         <v>0</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="48"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="85">
+        <f>(H6/31)*J6</f>
+        <v>22000</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>55</v>
+      <c r="A7" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="31">
+        <v>59</v>
+      </c>
+      <c r="E7" s="56">
         <v>44774</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="34">
+      <c r="F7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="57">
         <v>18000</v>
       </c>
       <c r="I7" s="15">
         <v>31</v>
       </c>
-      <c r="J7" s="15">
-        <f>Attandance!AI6</f>
-        <v>14</v>
-      </c>
-      <c r="K7" s="15">
+      <c r="J7" s="14">
+        <f>Attandance!AM6</f>
+        <v>31</v>
+      </c>
+      <c r="K7" s="14">
         <f>Attandance!AJ6</f>
         <v>0</v>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="14">
         <f>Attandance!AK6</f>
         <v>0</v>
       </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="49"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="72">
+        <f t="shared" ref="N7:N14" si="0">(H7/31)*J7</f>
+        <v>18000</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>56</v>
+      <c r="A8" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="31">
+        <v>59</v>
+      </c>
+      <c r="E8" s="56">
         <v>44774</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="34">
+      <c r="F8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="57">
         <v>15000</v>
       </c>
       <c r="I8" s="15">
         <v>31</v>
       </c>
-      <c r="J8" s="15">
-        <f>Attandance!AI7</f>
-        <v>14</v>
-      </c>
-      <c r="K8" s="15">
+      <c r="J8" s="14">
+        <f>Attandance!AM7</f>
+        <v>25</v>
+      </c>
+      <c r="K8" s="14">
         <f>Attandance!AJ7</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="35">
+        <v>6</v>
+      </c>
+      <c r="L8" s="14">
         <f>Attandance!AK7</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="49"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="72">
+        <f>(H8/30)*J8</f>
+        <v>12500</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>58</v>
+      <c r="A9" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="31">
+        <v>59</v>
+      </c>
+      <c r="E9" s="56">
         <v>45198</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="34">
+      <c r="F9" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="57">
         <v>15000</v>
       </c>
       <c r="I9" s="15">
         <v>31</v>
       </c>
-      <c r="J9" s="15">
-        <f>Attandance!AI8</f>
-        <v>13</v>
-      </c>
-      <c r="K9" s="15">
+      <c r="J9" s="14">
+        <v>29</v>
+      </c>
+      <c r="K9" s="14">
         <f>Attandance!AJ8</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="35">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
         <f>Attandance!AK8</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="49"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="72">
+        <f>(H9/30)*J9</f>
+        <v>14500</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>57</v>
+      <c r="A10" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="31">
+        <v>59</v>
+      </c>
+      <c r="E10" s="56">
         <v>45229</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="F10" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="57">
         <v>15000</v>
       </c>
       <c r="I10" s="15">
         <v>31</v>
       </c>
-      <c r="J10" s="15">
-        <f>Attandance!AI9</f>
-        <v>14</v>
-      </c>
-      <c r="K10" s="15">
+      <c r="J10" s="14">
+        <v>29</v>
+      </c>
+      <c r="K10" s="14">
         <f>Attandance!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="35">
+        <v>1</v>
+      </c>
+      <c r="L10" s="14">
         <f>Attandance!AK9</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="49"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="72">
+        <f>(H10/30)*J10</f>
+        <v>14500</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="31">
+      <c r="E11" s="56">
         <v>45323</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="34">
+      <c r="F11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="57">
         <v>25000</v>
       </c>
       <c r="I11" s="15">
         <v>31</v>
       </c>
-      <c r="J11" s="15">
-        <f>Attandance!AI10</f>
-        <v>14</v>
-      </c>
-      <c r="K11" s="15">
+      <c r="J11" s="14">
+        <f>Attandance!AM10</f>
+        <v>31</v>
+      </c>
+      <c r="K11" s="14">
         <f>Attandance!AJ10</f>
         <v>0</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="14">
         <f>Attandance!AK10</f>
         <v>0</v>
       </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="49"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="72">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>60</v>
+      <c r="A12" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="31">
+        <v>59</v>
+      </c>
+      <c r="E12" s="56">
         <v>45536</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="34">
+      <c r="F12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="57">
         <v>20000</v>
       </c>
       <c r="I12" s="15">
         <v>31</v>
       </c>
-      <c r="J12" s="15">
-        <f>Attandance!AI11</f>
-        <v>14</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="J12" s="14">
+        <f>Attandance!AM11</f>
+        <v>31</v>
+      </c>
+      <c r="K12" s="14">
         <f>Attandance!AJ11</f>
         <v>0</v>
       </c>
-      <c r="L12" s="35">
+      <c r="L12" s="14">
         <f>Attandance!AK11</f>
         <v>0</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="49"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="72">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
     </row>
-    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="53">
-        <v>45559</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="56">
-        <v>28000</v>
-      </c>
-      <c r="I13" s="52">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="56">
+        <v>45566</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="57">
+        <v>30000</v>
+      </c>
+      <c r="I13" s="15">
         <v>31</v>
       </c>
-      <c r="J13" s="52">
-        <f>Attandance!AI12</f>
-        <v>14</v>
-      </c>
-      <c r="K13" s="52">
+      <c r="J13" s="14">
+        <f>Attandance!AM12</f>
+        <v>9</v>
+      </c>
+      <c r="K13" s="14">
         <f>Attandance!AJ12</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="57">
+        <v>22</v>
+      </c>
+      <c r="L13" s="14">
         <f>Attandance!AK12</f>
         <v>0</v>
       </c>
-      <c r="M13" s="57"/>
-      <c r="N13" s="58"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="72">
+        <f>(H13/30)*J13</f>
+        <v>9000</v>
+      </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="61"/>
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="61">
+        <v>45559</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="62">
+        <v>28000</v>
+      </c>
+      <c r="I14" s="21">
+        <v>31</v>
+      </c>
+      <c r="J14" s="22">
+        <f>Attandance!AM13</f>
+        <v>31</v>
+      </c>
+      <c r="K14" s="22">
+        <f>Attandance!AJ13</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="22">
+        <f>Attandance!AK13</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="63"/>
+      <c r="N14" s="86">
+        <f t="shared" si="0"/>
+        <v>28000</v>
+      </c>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="32"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="40" t="s">
+      <c r="I18" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="45"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="46"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="45"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="46"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" s="44"/>
+      <c r="N19" s="34"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="31">
-        <v>44475</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="34">
-        <v>60000</v>
-      </c>
-      <c r="I20" s="15">
-        <v>31</v>
-      </c>
-      <c r="J20" s="15">
-        <f>Attandance!AI18</f>
-        <v>14</v>
-      </c>
-      <c r="K20" s="15">
-        <f>Attandance!AJ18</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="35">
-        <f>Attandance!AK18</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="48"/>
+    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="71"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="A21" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="81">
+        <v>44475</v>
+      </c>
+      <c r="F21" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="31">
-        <v>45468</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" s="34">
-        <v>24000</v>
-      </c>
-      <c r="I21" s="15">
+      <c r="G21" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="84">
+        <v>60000</v>
+      </c>
+      <c r="I21" s="80">
         <v>31</v>
       </c>
-      <c r="J21" s="15">
-        <f>Attandance!AI19</f>
-        <v>14</v>
-      </c>
-      <c r="K21" s="15">
+      <c r="J21" s="80">
+        <f>Attandance!AM19</f>
+        <v>29</v>
+      </c>
+      <c r="K21" s="80">
         <f>Attandance!AJ19</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="35">
+        <v>1</v>
+      </c>
+      <c r="L21" s="80">
         <f>Attandance!AK19</f>
         <v>0</v>
       </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="49"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="85">
+        <f>(H21/30)*J21</f>
+        <v>58000</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="16">
+        <v>45468</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="31">
-        <v>45505</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="34">
-        <v>8000</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="G22" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="19">
+        <v>24000</v>
+      </c>
+      <c r="I22" s="14">
         <v>31</v>
       </c>
-      <c r="J22" s="15">
-        <f>Attandance!AI20</f>
-        <v>14</v>
-      </c>
-      <c r="K22" s="15">
+      <c r="J22" s="14">
+        <f>Attandance!AM20</f>
+        <v>31</v>
+      </c>
+      <c r="K22" s="14">
         <f>Attandance!AJ20</f>
         <v>0</v>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="14">
         <f>Attandance!AK20</f>
         <v>0</v>
       </c>
-      <c r="M22" s="35"/>
-      <c r="N22" s="49"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="72">
+        <f>(H22/31)*J22</f>
+        <v>24000</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="16" t="s">
+      <c r="A23" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="16">
+        <v>45505</v>
+      </c>
+      <c r="F23" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="G23" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="19">
+        <v>8000</v>
+      </c>
+      <c r="I23" s="14">
         <v>31</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="31">
-        <v>44743</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="34">
-        <v>15000</v>
-      </c>
-      <c r="I23" s="15">
+      <c r="J23" s="14">
+        <f>Attandance!AM21</f>
         <v>31</v>
       </c>
-      <c r="J23" s="15">
-        <f>Attandance!AI21</f>
-        <v>6</v>
-      </c>
-      <c r="K23" s="15">
+      <c r="K23" s="14">
         <f>Attandance!AJ21</f>
-        <v>8</v>
-      </c>
-      <c r="L23" s="35">
+        <v>0</v>
+      </c>
+      <c r="L23" s="14">
         <f>Attandance!AK21</f>
         <v>0</v>
       </c>
-      <c r="M23" s="35"/>
-      <c r="N23" s="49"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="72">
+        <f>(H23/31)*J23</f>
+        <v>8000</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="16">
+        <v>44743</v>
+      </c>
+      <c r="F24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="G24" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="19">
+        <v>15000</v>
+      </c>
+      <c r="I24" s="14">
         <v>31</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="31">
-        <v>44967</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H24" s="34">
-        <v>15000</v>
-      </c>
-      <c r="I24" s="15">
-        <v>31</v>
-      </c>
-      <c r="J24" s="15">
-        <f>Attandance!AI22</f>
-        <v>14</v>
-      </c>
-      <c r="K24" s="15">
+      <c r="J24" s="14">
+        <f>Attandance!AM22</f>
+        <v>10</v>
+      </c>
+      <c r="K24" s="14">
         <f>Attandance!AJ22</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="35">
+        <v>21</v>
+      </c>
+      <c r="L24" s="14">
         <f>Attandance!AK22</f>
         <v>0</v>
       </c>
-      <c r="M24" s="35"/>
-      <c r="N24" s="49"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="72">
+        <f>(H24/30)*J24</f>
+        <v>5000</v>
+      </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="53">
-        <v>44959</v>
-      </c>
-      <c r="F25" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="56">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="16">
+        <v>44967</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="19">
         <v>15000</v>
       </c>
-      <c r="I25" s="52">
+      <c r="I25" s="14">
         <v>31</v>
       </c>
-      <c r="J25" s="52">
-        <f>Attandance!AI23</f>
-        <v>14</v>
-      </c>
-      <c r="K25" s="52">
+      <c r="J25" s="14">
+        <f>Attandance!AM23</f>
+        <v>31</v>
+      </c>
+      <c r="K25" s="14">
         <f>Attandance!AJ23</f>
         <v>0</v>
       </c>
-      <c r="L25" s="57">
+      <c r="L25" s="14">
         <f>Attandance!AK23</f>
         <v>0</v>
       </c>
-      <c r="M25" s="57"/>
-      <c r="N25" s="58"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="72">
+        <f>(H25/31)*J25</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="16">
+        <v>45587</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="19">
+        <v>15000</v>
+      </c>
+      <c r="I26" s="14">
+        <v>31</v>
+      </c>
+      <c r="J26" s="14">
+        <v>9</v>
+      </c>
+      <c r="K26" s="14">
+        <f>Attandance!AJ24</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="14">
+        <f>Attandance!AK24</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="72">
+        <f>(H26/30)*J26</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="61">
+        <v>44959</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="25">
+        <v>15000</v>
+      </c>
+      <c r="I27" s="22">
+        <v>31</v>
+      </c>
+      <c r="J27" s="22">
+        <f>Attandance!AM25</f>
+        <v>31</v>
+      </c>
+      <c r="K27" s="22">
+        <f>Attandance!AJ25</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="22">
+        <f>Attandance!AK25</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="86">
+        <f>(H27/31)*J27</f>
+        <v>15000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:M19"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="I3:L3"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="M3:M5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 C11:C12 B7:C10 D7:M13 D21:E24 G21:I24 F20:F25 K21:M25 D25:J25">
-    <cfRule type="expression" dxfId="2" priority="9">
+  <conditionalFormatting sqref="B6:M6 B7:C10 F21:F27 C11:C13 D22:E26 G22:I26 K22:M27 M7:M13 D7:L14 D27:J27">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>$C6=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20:B24 D20:E20 G20:M20 J21:J24">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$C20=#REF!</formula>
+  <conditionalFormatting sqref="C21:C27">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$C21=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:C25">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C20=#REF!</formula>
+  <conditionalFormatting sqref="D21:E21 G21:M21 B21:B26 J22:J26">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C21=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="N13" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Sindhi Muslim/Salary Sheet/Staff Record.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Staff Record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D25888A-7ED1-4A45-8209-D239927DDB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5877761-B516-4BA5-9D1A-8F32DB861640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="100">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>41105-4725771-0</t>
+  </si>
+  <si>
+    <t>0010108832370019</t>
   </si>
 </sst>
 </file>
@@ -847,75 +850,6 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -925,27 +859,12 @@
     <xf numFmtId="49" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -959,30 +878,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1018,17 +913,125 @@
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1404,11 +1407,11 @@
   <sheetData>
     <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="8" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -1533,13 +1536,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="28" t="s">
+      <c r="AI3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="29"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="54"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1644,19 +1647,19 @@
       <c r="AH4" s="9">
         <v>45596</v>
       </c>
-      <c r="AI4" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ4" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK4" s="77" t="s">
+      <c r="AI4" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AL4" s="77" t="s">
+      <c r="AL4" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="AM4" s="78" t="s">
+      <c r="AM4" s="42" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2480,98 +2483,98 @@
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A12" s="73">
-        <v>8</v>
-      </c>
-      <c r="B12" s="74" t="s">
+      <c r="A12" s="37">
+        <v>8</v>
+      </c>
+      <c r="B12" s="38" t="s">
         <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="T12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="U12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="V12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="W12" s="75"/>
-      <c r="X12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB12" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC12" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD12" s="75"/>
-      <c r="AE12" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF12" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG12" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH12" s="75" t="s">
+      <c r="D12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF12" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH12" s="39" t="s">
         <v>6</v>
       </c>
       <c r="AI12" s="10">
@@ -2713,11 +2716,11 @@
     </row>
     <row r="16" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="8" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Tue</v>
@@ -2842,13 +2845,13 @@
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AI17" s="28" t="s">
+      <c r="AI17" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="AJ17" s="28"/>
-      <c r="AK17" s="28"/>
-      <c r="AL17" s="28"/>
-      <c r="AM17" s="29"/>
+      <c r="AJ17" s="53"/>
+      <c r="AK17" s="53"/>
+      <c r="AL17" s="53"/>
+      <c r="AM17" s="54"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2953,19 +2956,19 @@
       <c r="AH18" s="9">
         <v>45596</v>
       </c>
-      <c r="AI18" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ18" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="77" t="s">
+      <c r="AI18" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ18" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK18" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AL18" s="77" t="s">
+      <c r="AL18" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="AM18" s="78" t="s">
+      <c r="AM18" s="42" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3555,117 +3558,117 @@
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A24" s="73">
-        <v>6</v>
-      </c>
-      <c r="B24" s="74" t="s">
+      <c r="A24" s="37">
+        <v>6</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>96</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="H24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75" t="s">
+      <c r="I24" s="39"/>
+      <c r="J24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="K24" s="75" t="s">
+      <c r="K24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="L24" s="75" t="s">
+      <c r="L24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="M24" s="75" t="s">
+      <c r="M24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="N24" s="75" t="s">
+      <c r="N24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="O24" s="75" t="s">
+      <c r="O24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75" t="s">
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="R24" s="75" t="s">
+      <c r="R24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="S24" s="75" t="s">
+      <c r="S24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="T24" s="75" t="s">
+      <c r="T24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="U24" s="75" t="s">
+      <c r="U24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="V24" s="75" t="s">
+      <c r="V24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="W24" s="75"/>
-      <c r="X24" s="75" t="s">
+      <c r="W24" s="39"/>
+      <c r="X24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="Y24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH24" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI24" s="75">
+      <c r="Y24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI24" s="39">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="AJ24" s="75">
+      <c r="AJ24" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="75">
+      <c r="AK24" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="75">
+      <c r="AL24" s="39">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="AM24" s="76">
+      <c r="AM24" s="40">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
@@ -3845,150 +3848,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="I3" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="58" t="s">
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="55" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="53" t="s">
+      <c r="A4" s="73"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="55" t="s">
+      <c r="K4" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="52"/>
-      <c r="N4" s="34"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="56"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="64"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="76"/>
       <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="71"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="57"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="45">
         <v>44774</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="83" t="s">
+      <c r="G6" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="48">
         <v>22000</v>
       </c>
-      <c r="I6" s="80">
+      <c r="I6" s="44">
         <v>31</v>
       </c>
-      <c r="J6" s="80">
+      <c r="J6" s="44">
         <f>Attandance!AM5</f>
         <v>31</v>
       </c>
-      <c r="K6" s="80">
+      <c r="K6" s="44">
         <f>Attandance!AJ5</f>
         <v>0</v>
       </c>
-      <c r="L6" s="80">
+      <c r="L6" s="44">
         <f>Attandance!AK5</f>
         <v>0</v>
       </c>
-      <c r="M6" s="80"/>
-      <c r="N6" s="85">
+      <c r="M6" s="44"/>
+      <c r="N6" s="49">
         <f>(H6/31)*J6</f>
         <v>22000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="31" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="15" t="s">
@@ -4000,7 +4003,7 @@
       <c r="D7" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="29">
         <v>44774</v>
       </c>
       <c r="F7" s="17" t="s">
@@ -4009,7 +4012,7 @@
       <c r="G7" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="30">
         <v>18000</v>
       </c>
       <c r="I7" s="15">
@@ -4028,13 +4031,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="15"/>
-      <c r="N7" s="72">
+      <c r="N7" s="36">
         <f t="shared" ref="N7:N14" si="0">(H7/31)*J7</f>
         <v>18000</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="31" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -4046,7 +4049,7 @@
       <c r="D8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="29">
         <v>44774</v>
       </c>
       <c r="F8" s="17" t="s">
@@ -4055,7 +4058,7 @@
       <c r="G8" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="30">
         <v>15000</v>
       </c>
       <c r="I8" s="15">
@@ -4074,13 +4077,13 @@
         <v>1</v>
       </c>
       <c r="M8" s="15"/>
-      <c r="N8" s="72">
+      <c r="N8" s="36">
         <f>(H8/30)*J8</f>
         <v>12500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="31" t="s">
         <v>63</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -4092,7 +4095,7 @@
       <c r="D9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="29">
         <v>45198</v>
       </c>
       <c r="F9" s="17" t="s">
@@ -4101,7 +4104,7 @@
       <c r="G9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="30">
         <v>15000</v>
       </c>
       <c r="I9" s="15">
@@ -4119,13 +4122,13 @@
         <v>1</v>
       </c>
       <c r="M9" s="15"/>
-      <c r="N9" s="72">
+      <c r="N9" s="36">
         <f>(H9/30)*J9</f>
         <v>14500</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="31" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4137,7 +4140,7 @@
       <c r="D10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="29">
         <v>45229</v>
       </c>
       <c r="F10" s="17" t="s">
@@ -4146,7 +4149,7 @@
       <c r="G10" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="30">
         <v>15000</v>
       </c>
       <c r="I10" s="15">
@@ -4164,13 +4167,13 @@
         <v>1</v>
       </c>
       <c r="M10" s="15"/>
-      <c r="N10" s="72">
+      <c r="N10" s="36">
         <f>(H10/30)*J10</f>
         <v>14500</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="31" t="s">
         <v>47</v>
       </c>
       <c r="B11" s="15" t="s">
@@ -4182,7 +4185,7 @@
       <c r="D11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="29">
         <v>45323</v>
       </c>
       <c r="F11" s="17" t="s">
@@ -4191,7 +4194,7 @@
       <c r="G11" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="30">
         <v>25000</v>
       </c>
       <c r="I11" s="15">
@@ -4210,13 +4213,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="15"/>
-      <c r="N11" s="72">
+      <c r="N11" s="36">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="31" t="s">
         <v>48</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4228,7 +4231,7 @@
       <c r="D12" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="29">
         <v>45536</v>
       </c>
       <c r="F12" s="17" t="s">
@@ -4237,7 +4240,7 @@
       <c r="G12" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="30">
         <v>20000</v>
       </c>
       <c r="I12" s="15">
@@ -4256,13 +4259,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="15"/>
-      <c r="N12" s="72">
+      <c r="N12" s="36">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="31" t="s">
         <v>91</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -4274,7 +4277,7 @@
       <c r="D13" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="29">
         <v>45566</v>
       </c>
       <c r="F13" s="17" t="s">
@@ -4283,7 +4286,7 @@
       <c r="G13" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="30">
         <v>30000</v>
       </c>
       <c r="I13" s="15">
@@ -4302,13 +4305,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="15"/>
-      <c r="N13" s="72">
+      <c r="N13" s="36">
         <f>(H13/30)*J13</f>
         <v>9000</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="32" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -4320,7 +4323,7 @@
       <c r="D14" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="33">
         <v>45559</v>
       </c>
       <c r="F14" s="23" t="s">
@@ -4329,7 +4332,7 @@
       <c r="G14" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="34">
         <v>28000</v>
       </c>
       <c r="I14" s="21">
@@ -4347,152 +4350,152 @@
         <f>Attandance!AK13</f>
         <v>1</v>
       </c>
-      <c r="M14" s="63"/>
-      <c r="N14" s="86">
+      <c r="M14" s="35"/>
+      <c r="N14" s="50">
         <f t="shared" si="0"/>
         <v>28000</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="32"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="79"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="43" t="s">
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="N18" s="33" t="s">
+      <c r="N18" s="55" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="35" t="s">
+      <c r="A19" s="73"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="37" t="s">
+      <c r="K19" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="L19" s="37" t="s">
+      <c r="L19" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="M19" s="44"/>
-      <c r="N19" s="34"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="56"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="64"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
       <c r="M20" s="91"/>
-      <c r="N20" s="71"/>
+      <c r="N20" s="57"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="45">
         <v>44475</v>
       </c>
-      <c r="F21" s="82" t="s">
+      <c r="F21" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="83" t="s">
+      <c r="G21" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="84">
+      <c r="H21" s="48">
         <v>60000</v>
       </c>
-      <c r="I21" s="80">
+      <c r="I21" s="44">
         <v>31</v>
       </c>
-      <c r="J21" s="80">
+      <c r="J21" s="44">
         <f>Attandance!AM19</f>
         <v>29</v>
       </c>
-      <c r="K21" s="80">
+      <c r="K21" s="44">
         <f>Attandance!AJ19</f>
         <v>1</v>
       </c>
-      <c r="L21" s="80">
+      <c r="L21" s="44">
         <f>Attandance!AK19</f>
         <v>0</v>
       </c>
-      <c r="M21" s="80"/>
-      <c r="N21" s="85">
+      <c r="M21" s="44"/>
+      <c r="N21" s="49">
         <f>(H21/30)*J21</f>
         <v>58000</v>
       </c>
@@ -4538,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="72">
+      <c r="N22" s="36">
         <f>(H22/31)*J22</f>
         <v>24000</v>
       </c>
@@ -4584,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="14"/>
-      <c r="N23" s="72">
+      <c r="N23" s="36">
         <f>(H23/31)*J23</f>
         <v>8000</v>
       </c>
@@ -4630,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="72">
+      <c r="N24" s="36">
         <f>(H24/30)*J24</f>
         <v>5000</v>
       </c>
@@ -4655,7 +4658,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="H25" s="19">
         <v>15000</v>
@@ -4676,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="72">
+      <c r="N25" s="36">
         <f>(H25/31)*J25</f>
         <v>15000</v>
       </c>
@@ -4685,7 +4688,7 @@
       <c r="A26" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="26" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="14" t="s">
@@ -4697,10 +4700,10 @@
       <c r="E26" s="16">
         <v>45587</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H26" s="19">
@@ -4721,13 +4724,13 @@
         <v>0</v>
       </c>
       <c r="M26" s="15"/>
-      <c r="N26" s="72">
+      <c r="N26" s="36">
         <f>(H26/30)*J26</f>
         <v>4500</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="32" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="21" t="s">
@@ -4739,7 +4742,7 @@
       <c r="D27" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="61">
+      <c r="E27" s="33">
         <v>44959</v>
       </c>
       <c r="F27" s="23" t="s">
@@ -4767,30 +4770,13 @@
         <v>0</v>
       </c>
       <c r="M27" s="22"/>
-      <c r="N27" s="86">
+      <c r="N27" s="50">
         <f>(H27/31)*J27</f>
         <v>15000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A16:N16"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="N18:N20"/>
     <mergeCell ref="I19:I20"/>
@@ -4806,19 +4792,36 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="D18:D20"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="J4:J5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 B7:C10 F21:F27 C11:C13 D22:E26 G22:I26 K22:M27 M7:M13 D7:L14 D27:J27">
-    <cfRule type="expression" dxfId="0" priority="9">
+  <conditionalFormatting sqref="B6:M6 B7:C10 M7:M13 D7:L14 C11:C13 F21:F27 D22:E26 G22:I26 K22:M27 D27:J27">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>$C6=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C27">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$C21=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21:E21 G21:M21 B21:B26 J22:J26">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$C21=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
